--- a/bounty/docs/PAR2-Data.xlsx
+++ b/bounty/docs/PAR2-Data.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="24">
   <si>
     <t xml:space="preserve">Bounty</t>
   </si>
@@ -76,16 +76,19 @@
     <t xml:space="preserve">UA</t>
   </si>
   <si>
-    <t xml:space="preserve">Total Tasks</t>
+    <t xml:space="preserve">#Total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#Solved</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Penalty</t>
   </si>
   <si>
     <t xml:space="preserve">#tasks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Penalty</t>
   </si>
   <si>
     <t xml:space="preserve">PAR-2</t>
@@ -121,7 +124,7 @@
       <family val="0"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -131,7 +134,31 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFCC"/>
+        <bgColor rgb="FFFFF1C1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF54B948"/>
+        <bgColor rgb="FF99CC00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.8"/>
+        <bgColor rgb="FFFFFF99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.8"/>
+        <bgColor rgb="FFFF99CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.4"/>
+        <bgColor rgb="FFFF6600"/>
       </patternFill>
     </fill>
   </fills>
@@ -169,7 +196,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="16">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -179,6 +206,58 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -191,6 +270,66 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFF1C1"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFB7E34"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFF5BBFE"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF54B948"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -308,12 +447,21 @@
   <dimension ref="A2:S19"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="7.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="7.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="6.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="7.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="9.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="7.37"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="6" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="6.51"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="8.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="7.3"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="8.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="6.7"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="8.25"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="15" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -659,60 +807,68 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C12" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="F12" s="1" t="s">
+      <c r="C12" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="I12" s="1" t="s">
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="L12" s="1" t="s">
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
+      <c r="M12" s="6"/>
+      <c r="N12" s="6"/>
+    </row>
+    <row r="13" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F13" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G13" s="1" t="s">
+      <c r="F13" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G13" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="H13" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I13" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J13" s="1" t="s">
+      <c r="I13" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="J13" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="K13" s="1" t="s">
+      <c r="K13" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="L13" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M13" s="1" t="s">
+      <c r="L13" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M13" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="N13" s="1" t="s">
+      <c r="N13" s="11" t="s">
         <v>21</v>
       </c>
     </row>
@@ -973,21 +1129,21 @@
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D19" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="D19" s="12" t="n">
         <f aca="false">(D18+E18)/B18</f>
         <v>38.0673276904474</v>
       </c>
-      <c r="G19" s="1" t="n">
+      <c r="G19" s="13" t="n">
         <f aca="false">(G18+H18)/B18</f>
         <v>146.250955259976</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="14" t="n">
         <f aca="false">(J18+K18)/B18</f>
         <v>214.077206771463</v>
       </c>
-      <c r="M19" s="1" t="n">
+      <c r="M19" s="15" t="n">
         <f aca="false">(M18+N18)/B18</f>
         <v>309.6646191052</v>
       </c>
